--- a/GameConfig/Datas/Defines/__enums__.xlsx
+++ b/GameConfig/Datas/Defines/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C23576E-56A3-4A21-AC06-4DFD4D062780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="4"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="1" r:id="rId1"/>
@@ -12,6 +18,7 @@
     <sheet name="音效枚举" sheetId="3" r:id="rId3"/>
     <sheet name="特效枚举" sheetId="4" r:id="rId4"/>
     <sheet name="语言地区" sheetId="5" r:id="rId5"/>
+    <sheet name="活动开启类型" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="85">
   <si>
     <t>##var</t>
   </si>
@@ -90,30 +97,6 @@
     <t>注释</t>
   </si>
   <si>
-    <t>test.AccessFlag</t>
-  </si>
-  <si>
-    <t>WRITE</t>
-  </si>
-  <si>
-    <t>READ</t>
-  </si>
-  <si>
-    <t>TRUNCATE</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>READ_WRITE</t>
-  </si>
-  <si>
-    <t>WRITE|READ</t>
-  </si>
-  <si>
-    <t>位标记使用示例</t>
-  </si>
-  <si>
     <t>ColorQuality</t>
   </si>
   <si>
@@ -247,19 +230,97 @@
   </si>
   <si>
     <t>占位符（新增+1）</t>
+  </si>
+  <si>
+    <t>ActivityOpenType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_FIXED</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定开启</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_TIME</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定时间开启</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_SVR_OPEN_TIME</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>开服时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_SVR_MEAGE_TIME</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合服时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_SVR_DAILY_TIME</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日固定时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_SVR_WEEK_TIME</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每周固定时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_CREATE_ROLE_DAY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>创角天数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_CREATE_ROLE_DAY_SECONDS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>按照当前创角时间开启活动 精确到秒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_SVR_WEEK_DURATION_TIME</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每周固定时间段</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_CLOSE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不开启</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,155 +332,19 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -428,198 +353,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799951170384838"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -642,255 +381,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -915,59 +412,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -980,6 +453,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1237,27 +713,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.8333333333333" customWidth="1"/>
-    <col min="4" max="5" width="14.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="9.33333333333333" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.0833333333333" customWidth="1"/>
-    <col min="11" max="11" width="15.0833333333333" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" customWidth="1"/>
+    <col min="11" max="11" width="15.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1279,15 +755,15 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -1313,7 +789,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
@@ -1343,89 +819,36 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="H7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" t="s">
-        <v>26</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.5833333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.58203125" style="1" customWidth="1"/>
     <col min="6" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="31.3333333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.0833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="37.3333333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="38.5833333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="33.5833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.08203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="37.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="38.58203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="33.58203125" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1447,15 +870,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1481,7 +904,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="85.5" spans="1:12">
+    <row r="3" spans="1:12" ht="84" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1511,9 +934,9 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -1522,144 +945,143 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J7" s="1">
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H8" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J8" s="1">
         <v>4</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H9" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H10" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J10" s="1">
         <v>6</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H11" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J11" s="1">
         <v>7</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H12" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="J12" s="1">
         <v>8</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="49.5" style="1" customWidth="1"/>
@@ -1669,12 +1091,12 @@
     <col min="8" max="8" width="21.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
     <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.3333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.75" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1696,15 +1118,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1730,7 +1152,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="57" spans="1:12">
+    <row r="3" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1760,9 +1182,9 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -1771,67 +1193,66 @@
         <v>1</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="J4" s="1">
         <v>1000001</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="J5" s="1">
         <v>1000002</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D1048576" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="40.0833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.08203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="69.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="42.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="24" style="1" customWidth="1"/>
     <col min="10" max="10" width="14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.0833333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.08203125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1853,15 +1274,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1887,7 +1308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="28.5" spans="1:12">
+    <row r="3" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1917,9 +1338,9 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -1928,19 +1349,19 @@
         <v>1</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="5"/>
       <c r="K5" s="5"/>
     </row>
@@ -1948,39 +1369,38 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H4:H5">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J5">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D5" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.66666666666667" style="1"/>
-    <col min="2" max="2" width="20.5833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.4166666666667" style="1" customWidth="1"/>
-    <col min="4" max="8" width="8.66666666666667" style="1"/>
-    <col min="9" max="9" width="28.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.66666666666667" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.4140625" style="1" customWidth="1"/>
+    <col min="4" max="8" width="8.6640625" style="1"/>
+    <col min="9" max="9" width="28.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="1"/>
     <col min="11" max="11" width="31.25" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.66666666666667" style="1"/>
+    <col min="12" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2002,15 +1422,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2036,7 +1456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="85.5" spans="1:12">
+    <row r="3" spans="1:12" ht="84" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2066,9 +1486,9 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -2077,126 +1497,388 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="J7" s="1">
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H8" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="J8" s="1">
         <v>4</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H9" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H10" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J10" s="1">
         <v>6</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H11" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J11" s="1">
         <v>7</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D4" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F8E00E-C676-4EBC-89F8-DBA46C4CF7FD}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="25.4140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.08203125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="8.6640625" style="1"/>
+    <col min="8" max="8" width="56.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="39.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="1"/>
+    <col min="11" max="11" width="44.33203125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="112" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="1">
+        <v>3</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="1">
+        <v>4</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" s="1">
+        <v>6</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="1">
+        <v>8</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="1">
+        <v>9</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/Defines/__enums__.xlsx
+++ b/GameConfig/Datas/Defines/__enums__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C23576E-56A3-4A21-AC06-4DFD4D062780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="1" r:id="rId1"/>
@@ -19,6 +13,9 @@
     <sheet name="特效枚举" sheetId="4" r:id="rId4"/>
     <sheet name="语言地区" sheetId="5" r:id="rId5"/>
     <sheet name="活动开启类型" sheetId="6" r:id="rId6"/>
+    <sheet name="玩家体型类型" sheetId="7" r:id="rId7"/>
+    <sheet name="活动类型枚举" sheetId="8" r:id="rId8"/>
+    <sheet name="系统开放类型" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -233,94 +230,154 @@
   </si>
   <si>
     <t>ActivityOpenType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_CLOSE</t>
+  </si>
+  <si>
+    <t>不开启</t>
   </si>
   <si>
     <t>ACTIVITY_OPEN_TYPE_FIXED</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>固定开启</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ACTIVITY_OPEN_TYPE_TIME</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>指定时间开启</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ACTIVITY_OPEN_TYPE_SVR_OPEN_TIME</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>开服时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ACTIVITY_OPEN_TYPE_SVR_MEAGE_TIME</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>合服时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ACTIVITY_OPEN_TYPE_SVR_DAILY_TIME</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>每日固定时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ACTIVITY_OPEN_TYPE_SVR_WEEK_TIME</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>每周固定时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTIVITY_OPEN_TYPE_SVR_WEEK_DURATION_TIME</t>
+  </si>
+  <si>
+    <t>每周固定时间段</t>
   </si>
   <si>
     <t>ACTIVITY_OPEN_TYPE_CREATE_ROLE_DAY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>创角天数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ACTIVITY_OPEN_TYPE_CREATE_ROLE_DAY_SECONDS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>按照当前创角时间开启活动 精确到秒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACTIVITY_OPEN_TYPE_SVR_WEEK_DURATION_TIME</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>每周固定时间段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACTIVITY_OPEN_TYPE_CLOSE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不开启</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleBodyType</t>
+  </si>
+  <si>
+    <t>ROLE_BODY_NONE</t>
+  </si>
+  <si>
+    <t>无定以体型</t>
+  </si>
+  <si>
+    <t>ROLE_BODY_MALE</t>
+  </si>
+  <si>
+    <t>男性体型</t>
+  </si>
+  <si>
+    <t>ROLE_BODY_FEMALE</t>
+  </si>
+  <si>
+    <t>女性体型</t>
+  </si>
+  <si>
+    <t>ActivityType</t>
+  </si>
+  <si>
+    <t>ACTIVITY_TYPE_NONE</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>FuncType</t>
+  </si>
+  <si>
+    <t>FUNC_TYPE_NONE</t>
+  </si>
+  <si>
+    <t>异常</t>
+  </si>
+  <si>
+    <t>FUNC_TYPE_SHOP</t>
+  </si>
+  <si>
+    <t>商城</t>
+  </si>
+  <si>
+    <t>FUNC_TYPE_ACTOR</t>
+  </si>
+  <si>
+    <t>角色</t>
+  </si>
+  <si>
+    <t>FUNC_TYPE_MAIN</t>
+  </si>
+  <si>
+    <t>主界面</t>
+  </si>
+  <si>
+    <t>FUNC_TYPE_LEAGUE</t>
+  </si>
+  <si>
+    <t>公会</t>
+  </si>
+  <si>
+    <t>FUNC_TYPE_GAMEPLAY</t>
+  </si>
+  <si>
+    <t>玩法</t>
+  </si>
+  <si>
+    <t>FUNC_TYPE_HOME</t>
+  </si>
+  <si>
+    <t>家园</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,19 +389,155 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,12 +546,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79992065187536243"/>
+        <fgColor theme="9" tint="0.799920651875362"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -381,9 +760,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -394,6 +1015,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -412,35 +1036,59 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -453,9 +1101,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -713,228 +1358,229 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="5" width="14.08203125" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.8333333333333" customWidth="1"/>
+    <col min="4" max="5" width="14.0833333333333" customWidth="1"/>
+    <col min="6" max="6" width="9.33333333333333" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.08203125" customWidth="1"/>
-    <col min="11" max="11" width="15.08203125" customWidth="1"/>
+    <col min="10" max="10" width="12.0833333333333" customWidth="1"/>
+    <col min="11" max="11" width="15.0833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6" t="s">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="6"/>
+      <c r="L3" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="20" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5833333333333" style="1" customWidth="1"/>
     <col min="6" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="31.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.08203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="37.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="38.58203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="33.58203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.3333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.0833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="37.3333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="38.5833333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="33.5833333333333" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="84" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="85.5" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
@@ -957,7 +1603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="H5" s="1" t="s">
         <v>22</v>
       </c>
@@ -971,7 +1617,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="H6" s="1" t="s">
         <v>24</v>
       </c>
@@ -985,7 +1631,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="H7" s="1" t="s">
         <v>26</v>
       </c>
@@ -999,7 +1645,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="H8" s="1" t="s">
         <v>28</v>
       </c>
@@ -1013,7 +1659,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="H9" s="1" t="s">
         <v>30</v>
       </c>
@@ -1027,7 +1673,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="H10" s="1" t="s">
         <v>32</v>
       </c>
@@ -1041,7 +1687,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="H11" s="1" t="s">
         <v>34</v>
       </c>
@@ -1055,7 +1701,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12">
       <c r="H12" s="1" t="s">
         <v>36</v>
       </c>
@@ -1073,15 +1719,16 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="49.5" style="1" customWidth="1"/>
@@ -1091,99 +1738,99 @@
     <col min="8" max="8" width="21.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
     <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.3333333333333" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.75" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="56" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="57" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="5" t="s">
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C4" s="1" t="b">
@@ -1192,24 +1839,24 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>39</v>
       </c>
       <c r="J4" s="1">
         <v>1000001</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H5" s="5" t="s">
+    <row r="5" spans="1:12">
+      <c r="H5" s="6" t="s">
         <v>41</v>
       </c>
       <c r="J5" s="1">
         <v>1000002</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="6" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1217,129 +1864,130 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D1048576" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D1048576">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="40.08203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.0833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="69.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.3333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="42.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="24" style="1" customWidth="1"/>
     <col min="10" max="10" width="14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.08203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.0833333333333" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="28.5" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="5" t="s">
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C4" s="1" t="b">
@@ -1348,146 +1996,147 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>45</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H5" s="5"/>
-      <c r="K5" s="5"/>
+    <row r="5" spans="1:12">
+      <c r="H5" s="6"/>
+      <c r="K5" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H4:H5">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J5">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D5" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D5">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.4140625" style="1" customWidth="1"/>
-    <col min="4" max="8" width="8.6640625" style="1"/>
-    <col min="9" max="9" width="28.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.66666666666667" style="1"/>
+    <col min="2" max="2" width="20.5833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.4166666666667" style="1" customWidth="1"/>
+    <col min="4" max="8" width="8.66666666666667" style="1"/>
+    <col min="9" max="9" width="28.8333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.66666666666667" style="1"/>
     <col min="11" max="11" width="31.25" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="1"/>
+    <col min="12" max="16384" width="8.66666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="84" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="85.5" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="1" t="b">
@@ -1496,34 +2145,34 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>48</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H5" s="4" t="s">
+    <row r="5" spans="1:12">
+      <c r="H5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>50</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="H6" s="1" t="s">
         <v>51</v>
       </c>
@@ -1537,7 +2186,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="H7" s="1" t="s">
         <v>53</v>
       </c>
@@ -1551,7 +2200,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="H8" s="1" t="s">
         <v>55</v>
       </c>
@@ -1565,7 +2214,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="H9" s="1" t="s">
         <v>57</v>
       </c>
@@ -1579,7 +2228,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="H10" s="1" t="s">
         <v>59</v>
       </c>
@@ -1593,7 +2242,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="H11" s="1" t="s">
         <v>61</v>
       </c>
@@ -1611,122 +2260,123 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D4" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D4">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F8E00E-C676-4EBC-89F8-DBA46C4CF7FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="25.4140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.08203125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="8.6640625" style="1"/>
-    <col min="8" max="8" width="56.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.66666666666667" style="1"/>
+    <col min="2" max="2" width="25.4166666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.8333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.0833333333333" style="1" customWidth="1"/>
+    <col min="6" max="7" width="8.66666666666667" style="1"/>
+    <col min="8" max="8" width="56.1666666666667" style="1" customWidth="1"/>
     <col min="9" max="9" width="39.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="1"/>
-    <col min="11" max="11" width="44.33203125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="1"/>
+    <col min="10" max="10" width="8.66666666666667" style="1"/>
+    <col min="11" max="11" width="44.3333333333333" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.66666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="112" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="128.25" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C4" s="1" t="b">
@@ -1735,150 +2385,672 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>84</v>
+      <c r="H4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="H5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="H7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="J7" s="1">
         <v>3</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="K7" s="5" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="H8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="J8" s="1">
         <v>4</v>
       </c>
-      <c r="K8" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H10" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" s="4" t="s">
+      <c r="K9" s="5" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="H10" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="J10" s="1">
         <v>6</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H11" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>82</v>
+      <c r="K10" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="H11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="H12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H12" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="J12" s="1">
         <v>8</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>80</v>
+      <c r="K12" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="H13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="J13" s="1">
         <v>9</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>80</v>
+      <c r="K13" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="28.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9" style="2"/>
+    <col min="4" max="4" width="25.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="21.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.75" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:12">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="171" spans="1:12">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="H5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="25.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.125" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="44.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="20.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23" style="2" customWidth="1"/>
+    <col min="11" max="11" width="37.125" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:12">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="85.5" spans="1:12">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="38.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="19.125" style="2" customWidth="1"/>
+    <col min="6" max="7" width="9" style="2"/>
+    <col min="8" max="8" width="44.125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="22" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="29.75" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:12">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="171" spans="1:12">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="H5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="H7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="H8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J8" s="2">
+        <v>4</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="2">
+        <v>5</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="H10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J10" s="2">
+        <v>6</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/Defines/__enums__.xlsx
+++ b/GameConfig/Datas/Defines/__enums__.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="8"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="1" r:id="rId1"/>
-    <sheet name="道具品质" sheetId="2" r:id="rId2"/>
-    <sheet name="音效枚举" sheetId="3" r:id="rId3"/>
-    <sheet name="特效枚举" sheetId="4" r:id="rId4"/>
-    <sheet name="语言地区" sheetId="5" r:id="rId5"/>
-    <sheet name="活动开启类型" sheetId="6" r:id="rId6"/>
-    <sheet name="玩家体型类型" sheetId="7" r:id="rId7"/>
-    <sheet name="活动类型枚举" sheetId="8" r:id="rId8"/>
-    <sheet name="系统开放类型" sheetId="9" r:id="rId9"/>
+    <sheet name="货币枚举" sheetId="10" r:id="rId2"/>
+    <sheet name="道具品质" sheetId="2" r:id="rId3"/>
+    <sheet name="音效枚举" sheetId="3" r:id="rId4"/>
+    <sheet name="特效枚举" sheetId="4" r:id="rId5"/>
+    <sheet name="语言地区" sheetId="5" r:id="rId6"/>
+    <sheet name="活动开启类型" sheetId="6" r:id="rId7"/>
+    <sheet name="玩家体型类型" sheetId="7" r:id="rId8"/>
+    <sheet name="活动类型枚举" sheetId="8" r:id="rId9"/>
+    <sheet name="系统开放类型" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="121">
   <si>
     <t>##var</t>
   </si>
@@ -94,6 +95,45 @@
     <t>注释</t>
   </si>
   <si>
+    <t>CurrencyType</t>
+  </si>
+  <si>
+    <t>CURRENCY_NONE</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>CURRENCY_GOLD</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>CURRENCY_DIAMOND</t>
+  </si>
+  <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>CURRENCY_STAM</t>
+  </si>
+  <si>
+    <t>体力</t>
+  </si>
+  <si>
+    <t>CURRENCY_EXP</t>
+  </si>
+  <si>
+    <t>经验</t>
+  </si>
+  <si>
+    <t>CURRENCY_MAX</t>
+  </si>
+  <si>
+    <t>最大</t>
+  </si>
+  <si>
     <t>ColorQuality</t>
   </si>
   <si>
@@ -223,9 +263,6 @@
     <t>MAX</t>
   </si>
   <si>
-    <t>最大</t>
-  </si>
-  <si>
     <t>占位符（新增+1）</t>
   </si>
   <si>
@@ -317,9 +354,6 @@
   </si>
   <si>
     <t>ACTIVITY_TYPE_NONE</t>
-  </si>
-  <si>
-    <t>无</t>
   </si>
   <si>
     <t>FuncType</t>
@@ -377,14 +411,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -878,154 +905,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1379,90 +1400,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7" t="s">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="7"/>
+      <c r="L3" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1474,7 +1495,433 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="38.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="19.125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="44.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.75" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:12">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="171" spans="1:12">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="H5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="H7" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J7" s="1">
+        <v>3</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="H8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J8" s="1">
+        <v>4</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="H10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J10" s="1">
+        <v>6</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="14.75" style="1" customWidth="1"/>
+    <col min="5" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="32.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="99" customHeight="1" spans="1:12">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="H5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="H7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="1">
+        <v>3</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="H8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="1">
+        <v>4</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L12"/>
@@ -1495,94 +1942,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="85.5" spans="1:12">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -1591,128 +2038,128 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J7" s="1">
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J8" s="1">
         <v>4</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="H9" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="H10" s="1" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="J10" s="1">
         <v>6</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="H11" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="J11" s="1">
         <v>7</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="H12" s="1" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="J12" s="1">
         <v>8</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1724,7 +2171,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L5"/>
@@ -1744,94 +2191,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="57" spans="1:12">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="B4" s="6" t="s">
-        <v>38</v>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -1839,25 +2286,25 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>39</v>
+      <c r="H4" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="J4" s="1">
         <v>1000001</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>40</v>
+      <c r="K4" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="H5" s="6" t="s">
-        <v>41</v>
+      <c r="H5" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="J5" s="1">
         <v>1000002</v>
       </c>
-      <c r="K5" s="6" t="s">
-        <v>42</v>
+      <c r="K5" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1880,7 +2327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L5"/>
@@ -1901,94 +2348,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="28.5" spans="1:12">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="B4" s="6" t="s">
-        <v>43</v>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -1996,22 +2443,22 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>45</v>
+      <c r="H4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>45</v>
+      <c r="K4" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="H5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="H5" s="4"/>
+      <c r="K5" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2033,7 +2480,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L11"/>
@@ -2050,94 +2497,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="85.5" spans="1:12">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="B4" s="5" t="s">
-        <v>46</v>
+      <c r="B4" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -2145,115 +2592,115 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>48</v>
+      <c r="H4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>48</v>
+      <c r="K4" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="H5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>50</v>
+      <c r="H5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>50</v>
+      <c r="K5" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="J7" s="1">
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J8" s="1">
         <v>4</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="H9" s="1" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="H10" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="J10" s="1">
         <v>6</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="H11" s="1" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="J11" s="1">
         <v>7</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2270,7 +2717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L13"/>
@@ -2290,94 +2737,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="128.25" spans="1:12">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="B4" s="5" t="s">
-        <v>64</v>
+      <c r="B4" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -2385,143 +2832,143 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>66</v>
+      <c r="H4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>66</v>
+      <c r="K4" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="H5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>68</v>
+      <c r="H5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>68</v>
+      <c r="K5" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="H6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>70</v>
+      <c r="H6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>70</v>
+      <c r="K6" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="H7" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>72</v>
+      <c r="H7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="J7" s="1">
         <v>3</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>72</v>
+      <c r="K7" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="H8" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>74</v>
+      <c r="H8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="J8" s="1">
         <v>4</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>74</v>
+      <c r="K8" s="4" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="H9" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>76</v>
+      <c r="H9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>76</v>
+      <c r="K9" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="H10" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>78</v>
+      <c r="H10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="J10" s="1">
         <v>6</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>78</v>
+      <c r="K10" s="4" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="H11" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>80</v>
+      <c r="H11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>80</v>
+      <c r="K11" s="4" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="H12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>82</v>
+      <c r="H12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="J12" s="1">
         <v>8</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>82</v>
+      <c r="K12" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="H13" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>84</v>
+      <c r="H13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="J13" s="1">
         <v>9</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>84</v>
+      <c r="K13" s="4" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2533,297 +2980,161 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="28.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="25.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="21.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="20.375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.75" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="28.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="25.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="21.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.75" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="171" spans="1:12">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="B4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="b">
+      <c r="B4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>87</v>
+      <c r="H4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="H5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="H5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="1">
         <v>1</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>89</v>
+      <c r="K5" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="H6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="H6" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J6" s="1">
         <v>2</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
-  <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="25.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.125" style="2" customWidth="1"/>
-    <col min="5" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="44.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20.875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23" style="2" customWidth="1"/>
-    <col min="11" max="11" width="37.125" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="85.5" spans="1:12">
-      <c r="A3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>94</v>
+      <c r="K6" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2838,212 +3149,128 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="38.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="19.125" style="2" customWidth="1"/>
-    <col min="6" max="7" width="9" style="2"/>
-    <col min="8" max="8" width="44.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="22" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="29.75" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="25.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="44.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23" style="1" customWidth="1"/>
+    <col min="11" max="11" width="37.125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:12">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="171" spans="1:12">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="1" customFormat="1" ht="85.5" spans="1:12">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="B4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="b">
+      <c r="B4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="H5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="H6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J6" s="2">
-        <v>2</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="H7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J7" s="2">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="H8" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J8" s="2">
-        <v>4</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="H9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J9" s="2">
-        <v>5</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="H10" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J10" s="2">
-        <v>6</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>109</v>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/Defines/__enums__.xlsx
+++ b/GameConfig/Datas/Defines/__enums__.xlsx
@@ -4,19 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="1" r:id="rId1"/>
     <sheet name="货币枚举" sheetId="10" r:id="rId2"/>
-    <sheet name="道具品质" sheetId="2" r:id="rId3"/>
-    <sheet name="音效枚举" sheetId="3" r:id="rId4"/>
-    <sheet name="特效枚举" sheetId="4" r:id="rId5"/>
-    <sheet name="语言地区" sheetId="5" r:id="rId6"/>
-    <sheet name="活动开启类型" sheetId="6" r:id="rId7"/>
-    <sheet name="玩家体型类型" sheetId="7" r:id="rId8"/>
-    <sheet name="活动类型枚举" sheetId="8" r:id="rId9"/>
-    <sheet name="系统开放类型" sheetId="9" r:id="rId10"/>
+    <sheet name="音效枚举" sheetId="3" r:id="rId3"/>
+    <sheet name="特效枚举" sheetId="4" r:id="rId4"/>
+    <sheet name="语言地区" sheetId="5" r:id="rId5"/>
+    <sheet name="活动开启类型" sheetId="6" r:id="rId6"/>
+    <sheet name="活动类型枚举" sheetId="8" r:id="rId7"/>
+    <sheet name="系统开放类型" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -95,9 +93,96 @@
     <t>注释</t>
   </si>
   <si>
+    <t>RoleBodyType</t>
+  </si>
+  <si>
+    <t>玩家性别体型</t>
+  </si>
+  <si>
+    <t>ROLE_BODY_NONE</t>
+  </si>
+  <si>
+    <t>无定以体型</t>
+  </si>
+  <si>
+    <t>ROLE_BODY_MALE</t>
+  </si>
+  <si>
+    <t>男性体型</t>
+  </si>
+  <si>
+    <t>ROLE_BODY_FEMALE</t>
+  </si>
+  <si>
+    <t>女性体型</t>
+  </si>
+  <si>
+    <t>ColorQuality</t>
+  </si>
+  <si>
+    <t>道具品质颜色</t>
+  </si>
+  <si>
+    <t>COLOR_NONE</t>
+  </si>
+  <si>
+    <t>无定义颜色占位</t>
+  </si>
+  <si>
+    <t>COLOR_WHITE</t>
+  </si>
+  <si>
+    <t>白色</t>
+  </si>
+  <si>
+    <t>COLOR_GREEN</t>
+  </si>
+  <si>
+    <t>绿色</t>
+  </si>
+  <si>
+    <t>COLOR_BLUE</t>
+  </si>
+  <si>
+    <t>蓝色</t>
+  </si>
+  <si>
+    <t>COLOR_PURPLE</t>
+  </si>
+  <si>
+    <t>紫色</t>
+  </si>
+  <si>
+    <t>COLOR_ORANGE</t>
+  </si>
+  <si>
+    <t>橙色</t>
+  </si>
+  <si>
+    <t>COLOR_RED</t>
+  </si>
+  <si>
+    <t>红色</t>
+  </si>
+  <si>
+    <t>COLOR_CAI</t>
+  </si>
+  <si>
+    <t>彩色</t>
+  </si>
+  <si>
+    <t>COLOR_MAX</t>
+  </si>
+  <si>
+    <t>最大品质，新增+1</t>
+  </si>
+  <si>
     <t>CurrencyType</t>
   </si>
   <si>
+    <t>货币枚举类型</t>
+  </si>
+  <si>
     <t>CURRENCY_NONE</t>
   </si>
   <si>
@@ -134,66 +219,12 @@
     <t>最大</t>
   </si>
   <si>
-    <t>ColorQuality</t>
-  </si>
-  <si>
-    <t>COLOR_NONE</t>
-  </si>
-  <si>
-    <t>无定义颜色占位</t>
-  </si>
-  <si>
-    <t>COLOR_WHITE</t>
-  </si>
-  <si>
-    <t>白色</t>
-  </si>
-  <si>
-    <t>COLOR_GREEN</t>
-  </si>
-  <si>
-    <t>绿色</t>
-  </si>
-  <si>
-    <t>COLOR_BLUE</t>
-  </si>
-  <si>
-    <t>蓝色</t>
-  </si>
-  <si>
-    <t>COLOR_PURPLE</t>
-  </si>
-  <si>
-    <t>紫色</t>
-  </si>
-  <si>
-    <t>COLOR_ORANGE</t>
-  </si>
-  <si>
-    <t>橙色</t>
-  </si>
-  <si>
-    <t>COLOR_RED</t>
-  </si>
-  <si>
-    <t>红色</t>
-  </si>
-  <si>
-    <t>COLOR_CAI</t>
-  </si>
-  <si>
-    <t>彩色</t>
-  </si>
-  <si>
-    <t>COLOR_MAX</t>
-  </si>
-  <si>
-    <t>最大品质，新增+1</t>
-  </si>
-  <si>
     <t>SysSoundID</t>
   </si>
   <si>
+    <t>音效枚举</t>
+  </si>
+  <si>
     <t>BGM</t>
   </si>
   <si>
@@ -209,6 +240,9 @@
     <t>CommonEffectID</t>
   </si>
   <si>
+    <t>特效枚举</t>
+  </si>
+  <si>
     <t>COMMON_EFFECT_1</t>
   </si>
   <si>
@@ -218,6 +252,9 @@
     <t>LocalAreaType</t>
   </si>
   <si>
+    <t>语言地区枚举</t>
+  </si>
+  <si>
     <t>CN</t>
   </si>
   <si>
@@ -269,6 +306,9 @@
     <t>ActivityOpenType</t>
   </si>
   <si>
+    <t>活动开启类型</t>
+  </si>
+  <si>
     <t>ACTIVITY_OPEN_TYPE_CLOSE</t>
   </si>
   <si>
@@ -329,34 +369,19 @@
     <t>按照当前创角时间开启活动 精确到秒</t>
   </si>
   <si>
-    <t>RoleBodyType</t>
-  </si>
-  <si>
-    <t>ROLE_BODY_NONE</t>
-  </si>
-  <si>
-    <t>无定以体型</t>
-  </si>
-  <si>
-    <t>ROLE_BODY_MALE</t>
-  </si>
-  <si>
-    <t>男性体型</t>
-  </si>
-  <si>
-    <t>ROLE_BODY_FEMALE</t>
-  </si>
-  <si>
-    <t>女性体型</t>
-  </si>
-  <si>
     <t>ActivityType</t>
   </si>
   <si>
+    <t>活动类型枚举</t>
+  </si>
+  <si>
     <t>ACTIVITY_TYPE_NONE</t>
   </si>
   <si>
     <t>FuncType</t>
+  </si>
+  <si>
+    <t>系统开放类型</t>
   </si>
   <si>
     <t>FUNC_TYPE_NONE</t>
@@ -1051,11 +1076,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1385,40 +1410,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.8333333333333" customWidth="1"/>
-    <col min="4" max="5" width="14.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="9.33333333333333" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.0833333333333" customWidth="1"/>
-    <col min="11" max="11" width="15.0833333333333" customWidth="1"/>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="19" style="5" customWidth="1"/>
+    <col min="3" max="3" width="20.8333333333333" style="5" customWidth="1"/>
+    <col min="4" max="5" width="14.0833333333333" style="5" customWidth="1"/>
+    <col min="6" max="6" width="30" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.25" style="5" customWidth="1"/>
+    <col min="8" max="8" width="32.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="37.25" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="36.25" style="5" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -1430,60 +1457,262 @@
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="5"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:12">
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:12">
+      <c r="H5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:12">
+      <c r="H6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:12">
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:12">
+      <c r="H10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:12">
+      <c r="H11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:12">
+      <c r="H12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="1">
+        <v>3</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:12">
+      <c r="H13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="1">
+        <v>4</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:12">
+      <c r="H14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="1">
+        <v>5</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:12">
+      <c r="H15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="1">
+        <v>6</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:12">
+      <c r="H16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="1">
+        <v>7</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="8:11">
+      <c r="H17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="1">
+        <v>8</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1491,226 +1720,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="38.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="19.125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="44.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.75" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="171" spans="1:12">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="H5" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="H6" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="H7" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="J7" s="1">
-        <v>3</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="H8" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J8" s="1">
-        <v>4</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="H9" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J9" s="1">
-        <v>5</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="H10" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J10" s="1">
-        <v>6</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1725,7 +1734,9 @@
     <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
     <col min="4" max="4" width="14.75" style="1" customWidth="1"/>
-    <col min="5" max="7" width="9" style="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="31" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
     <col min="8" max="8" width="32.125" style="1" customWidth="1"/>
     <col min="9" max="9" width="24.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="16.875" style="1" customWidth="1"/>
@@ -1821,7 +1832,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -1829,87 +1840,90 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="H4" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="1" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" s="1" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" s="1" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="J7" s="1">
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="J8" s="1">
         <v>4</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="H9" s="1" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1924,256 +1938,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.5833333333333" style="1" customWidth="1"/>
-    <col min="6" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="31.3333333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.0833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="37.3333333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="38.5833333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="33.5833333333333" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="85.5" spans="1:12">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="H5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="H6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="H7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="1">
-        <v>3</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="H8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="1">
-        <v>4</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="H9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="1">
-        <v>5</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="H10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="1">
-        <v>6</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="H11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="1">
-        <v>7</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="H12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J12" s="1">
-        <v>8</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
@@ -2181,7 +1945,9 @@
     <col min="2" max="2" width="49.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="1" customWidth="1"/>
-    <col min="5" max="7" width="9" style="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="19.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
     <col min="8" max="8" width="21.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
     <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
@@ -2278,7 +2044,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -2286,25 +2052,28 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="H4" s="4" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="J4" s="1">
         <v>1000001</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="J5" s="1">
         <v>1000002</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2327,7 +2096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L5"/>
@@ -2435,7 +2204,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -2443,17 +2212,20 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="H4" s="4" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2480,7 +2252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L11"/>
@@ -2489,7 +2261,9 @@
     <col min="1" max="1" width="8.66666666666667" style="1"/>
     <col min="2" max="2" width="20.5833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.4166666666667" style="1" customWidth="1"/>
-    <col min="4" max="8" width="8.66666666666667" style="1"/>
+    <col min="4" max="5" width="8.66666666666667" style="1"/>
+    <col min="6" max="6" width="27.5" style="1" customWidth="1"/>
+    <col min="7" max="8" width="8.66666666666667" style="1"/>
     <col min="9" max="9" width="28.8333333333333" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.66666666666667" style="1"/>
     <col min="11" max="11" width="31.25" style="1" customWidth="1"/>
@@ -2584,7 +2358,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="4" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -2592,115 +2366,118 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="H4" s="4" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" s="1" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="J7" s="1">
         <v>3</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" s="1" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J8" s="1">
         <v>4</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="H9" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="H10" s="1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J10" s="1">
         <v>6</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="H11" s="1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="J11" s="1">
         <v>7</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2717,7 +2494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L13"/>
@@ -2727,8 +2504,9 @@
     <col min="2" max="2" width="25.4166666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.3333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.8333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.0833333333333" style="1" customWidth="1"/>
-    <col min="6" max="7" width="8.66666666666667" style="1"/>
+    <col min="5" max="5" width="9.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.66666666666667" style="1"/>
     <col min="8" max="8" width="56.1666666666667" style="1" customWidth="1"/>
     <col min="9" max="9" width="39.75" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.66666666666667" style="1"/>
@@ -2824,7 +2602,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="4" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -2832,143 +2610,146 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="H4" s="4" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" s="4" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" s="4" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J7" s="1">
         <v>3</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" s="4" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="J8" s="1">
         <v>4</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="H9" s="4" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="H10" s="4" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="J10" s="1">
         <v>6</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="H11" s="4" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="J11" s="1">
         <v>7</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="H12" s="4" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="J12" s="1">
         <v>8</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="H13" s="4" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="J13" s="1">
         <v>9</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2980,173 +2761,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
-  <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="28.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="25.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="21.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.75" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="171" spans="1:12">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="H5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="H6" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L4"/>
@@ -3156,7 +2771,9 @@
     <col min="2" max="2" width="25.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.125" style="1" customWidth="1"/>
-    <col min="5" max="7" width="9" style="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="26.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
     <col min="8" max="8" width="44.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="23" style="1" customWidth="1"/>
@@ -3252,7 +2869,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -3260,17 +2877,245 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="H4" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>21</v>
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="38.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="44.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.75" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:12">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="171" spans="1:12">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="H5" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="H7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" s="1">
+        <v>3</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="H8" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J8" s="1">
+        <v>4</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="H9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="H10" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J10" s="1">
+        <v>6</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/Defines/__enums__.xlsx
+++ b/GameConfig/Datas/Defines/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FAB997-2F4E-4AEA-A8B2-C61394F9D19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="5"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="1" r:id="rId1"/>
@@ -429,14 +435,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,151 +445,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -598,198 +461,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799920651875362"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79989013336588644"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -812,255 +489,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1082,59 +517,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1147,6 +558,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1404,29 +818,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
     <col min="2" max="2" width="19" style="5" customWidth="1"/>
-    <col min="3" max="3" width="20.8333333333333" style="5" customWidth="1"/>
-    <col min="4" max="5" width="14.0833333333333" style="5" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="5" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" style="5" customWidth="1"/>
     <col min="6" max="6" width="30" style="5" customWidth="1"/>
     <col min="7" max="7" width="12.25" style="5" customWidth="1"/>
-    <col min="8" max="8" width="32.625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="32.58203125" style="5" customWidth="1"/>
     <col min="9" max="9" width="37.25" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="5" customWidth="1"/>
     <col min="11" max="11" width="36.25" style="5" customWidth="1"/>
     <col min="12" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1448,15 +862,15 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -1482,7 +896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
@@ -1512,7 +926,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:12">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1538,7 +952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:12">
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H5" s="1" t="s">
         <v>23</v>
       </c>
@@ -1552,7 +966,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:12">
+    <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1566,17 +980,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:12">
+    <row r="9" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>27</v>
       </c>
@@ -1602,7 +1016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:12">
+    <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H10" s="1" t="s">
         <v>31</v>
       </c>
@@ -1616,7 +1030,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:12">
+    <row r="11" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H11" s="1" t="s">
         <v>33</v>
       </c>
@@ -1630,7 +1044,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:12">
+    <row r="12" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H12" s="1" t="s">
         <v>35</v>
       </c>
@@ -1644,7 +1058,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:12">
+    <row r="13" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H13" s="1" t="s">
         <v>37</v>
       </c>
@@ -1658,7 +1072,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:12">
+    <row r="14" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H14" s="1" t="s">
         <v>39</v>
       </c>
@@ -1672,7 +1086,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:12">
+    <row r="15" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H15" s="1" t="s">
         <v>41</v>
       </c>
@@ -1686,7 +1100,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:12">
+    <row r="16" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H16" s="1" t="s">
         <v>43</v>
       </c>
@@ -1700,7 +1114,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="8:11">
+    <row r="17" spans="8:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H17" s="1" t="s">
         <v>45</v>
       </c>
@@ -1718,17 +1132,16 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
@@ -1737,14 +1150,14 @@
     <col min="5" max="5" width="9" style="1"/>
     <col min="6" max="6" width="31" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="32.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.08203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="24.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="27.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.08203125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1766,15 +1179,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1800,7 +1213,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1830,7 +1243,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>47</v>
       </c>
@@ -1856,7 +1269,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="1" t="s">
         <v>51</v>
       </c>
@@ -1870,7 +1283,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" s="1" t="s">
         <v>53</v>
       </c>
@@ -1884,7 +1297,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="1" t="s">
         <v>55</v>
       </c>
@@ -1898,7 +1311,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H8" s="1" t="s">
         <v>57</v>
       </c>
@@ -1912,7 +1325,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H9" s="1" t="s">
         <v>59</v>
       </c>
@@ -1930,33 +1343,32 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="49.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="19.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
     <col min="8" max="8" width="21.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
     <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.3333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.75" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1978,15 +1390,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2012,7 +1424,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="57" spans="1:12">
+    <row r="3" spans="1:12" ht="56" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2042,7 +1454,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>61</v>
       </c>
@@ -2065,7 +1477,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="4" t="s">
         <v>65</v>
       </c>
@@ -2080,43 +1492,42 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D1048576" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="40.0833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.08203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="69.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="42.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="24" style="1" customWidth="1"/>
     <col min="10" max="10" width="14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.0833333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.08203125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2138,15 +1549,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2172,7 +1583,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="28.5" spans="1:12">
+    <row r="3" spans="1:12" ht="28" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2202,7 +1613,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>67</v>
       </c>
@@ -2228,7 +1639,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="4"/>
       <c r="K5" s="4"/>
     </row>
@@ -2236,41 +1647,40 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H4:H5">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J5">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D5" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.66666666666667" style="1"/>
-    <col min="2" max="2" width="20.5833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.4166666666667" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.66666666666667" style="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="20.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.4140625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.6640625" style="1"/>
     <col min="6" max="6" width="27.5" style="1" customWidth="1"/>
-    <col min="7" max="8" width="8.66666666666667" style="1"/>
-    <col min="9" max="9" width="28.8333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.66666666666667" style="1"/>
+    <col min="7" max="8" width="8.6640625" style="1"/>
+    <col min="9" max="9" width="28.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="1"/>
     <col min="11" max="11" width="31.25" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.66666666666667" style="1"/>
+    <col min="12" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2292,15 +1702,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2326,7 +1736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="85.5" spans="1:12">
+    <row r="3" spans="1:12" ht="84" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2356,7 +1766,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>71</v>
       </c>
@@ -2382,7 +1792,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="4" t="s">
         <v>75</v>
       </c>
@@ -2396,7 +1806,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" s="1" t="s">
         <v>77</v>
       </c>
@@ -2410,7 +1820,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="1" t="s">
         <v>79</v>
       </c>
@@ -2424,7 +1834,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H8" s="1" t="s">
         <v>81</v>
       </c>
@@ -2438,7 +1848,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H9" s="1" t="s">
         <v>83</v>
       </c>
@@ -2452,7 +1862,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H10" s="1" t="s">
         <v>85</v>
       </c>
@@ -2466,7 +1876,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H11" s="1" t="s">
         <v>87</v>
       </c>
@@ -2484,37 +1894,36 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D4" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.66666666666667" style="1"/>
-    <col min="2" max="2" width="25.4166666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.8333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="1"/>
+    <col min="2" max="2" width="25.4140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="26.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.66666666666667" style="1"/>
-    <col min="8" max="8" width="56.1666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="1"/>
+    <col min="8" max="8" width="56.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="39.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.66666666666667" style="1"/>
-    <col min="11" max="11" width="44.3333333333333" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.66666666666667" style="1"/>
+    <col min="10" max="10" width="8.6640625" style="1"/>
+    <col min="11" max="11" width="44.33203125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2536,15 +1945,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2570,7 +1979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="128.25" spans="1:12">
+    <row r="3" spans="1:12" ht="112" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2600,7 +2009,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>89</v>
       </c>
@@ -2626,7 +2035,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="4" t="s">
         <v>93</v>
       </c>
@@ -2640,7 +2049,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" s="4" t="s">
         <v>95</v>
       </c>
@@ -2654,7 +2063,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="4" t="s">
         <v>97</v>
       </c>
@@ -2668,7 +2077,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H8" s="4" t="s">
         <v>99</v>
       </c>
@@ -2682,7 +2091,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H9" s="4" t="s">
         <v>101</v>
       </c>
@@ -2696,7 +2105,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H10" s="4" t="s">
         <v>103</v>
       </c>
@@ -2710,7 +2119,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H11" s="4" t="s">
         <v>105</v>
       </c>
@@ -2724,7 +2133,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H12" s="4" t="s">
         <v>107</v>
       </c>
@@ -2738,7 +2147,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H13" s="4" t="s">
         <v>109</v>
       </c>
@@ -2756,32 +2165,31 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="25.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1"/>
     <col min="6" max="6" width="26.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
     <col min="8" max="8" width="44.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="23" style="1" customWidth="1"/>
-    <col min="11" max="11" width="37.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="37.08203125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2803,15 +2211,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2837,7 +2245,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="85.5" spans="1:12">
+    <row r="3" spans="1:12" ht="70" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2867,7 +2275,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>111</v>
       </c>
@@ -2897,32 +2305,31 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="38.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.58203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.08203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.08203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="44.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="44.08203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="22" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="29.75" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2944,15 +2351,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2978,7 +2385,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="171" spans="1:12">
+    <row r="3" spans="1:12" ht="168" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -3008,7 +2415,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>114</v>
       </c>
@@ -3034,7 +2441,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="1" t="s">
         <v>118</v>
       </c>
@@ -3048,7 +2455,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" s="1" t="s">
         <v>120</v>
       </c>
@@ -3062,7 +2469,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="1" t="s">
         <v>122</v>
       </c>
@@ -3076,7 +2483,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H8" s="1" t="s">
         <v>124</v>
       </c>
@@ -3090,7 +2497,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H9" s="1" t="s">
         <v>126</v>
       </c>
@@ -3104,7 +2511,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H10" s="1" t="s">
         <v>128</v>
       </c>
@@ -3122,7 +2529,7 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/Defines/__enums__.xlsx
+++ b/GameConfig/Datas/Defines/__enums__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5FAB997-2F4E-4AEA-A8B2-C61394F9D19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="1" r:id="rId1"/>
@@ -21,6 +15,7 @@
     <sheet name="活动开启类型" sheetId="6" r:id="rId6"/>
     <sheet name="活动类型枚举" sheetId="8" r:id="rId7"/>
     <sheet name="系统开放类型" sheetId="9" r:id="rId8"/>
+    <sheet name="怪物类型" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="137">
   <si>
     <t>##var</t>
   </si>
@@ -430,13 +425,40 @@
   </si>
   <si>
     <t>家园</t>
+  </si>
+  <si>
+    <t>MonsterType</t>
+  </si>
+  <si>
+    <t>怪物类型</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>普通怪物</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>精英</t>
+  </si>
+  <si>
+    <t>Boss</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,14 +467,151 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,12 +620,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79989013336588644"/>
+        <fgColor theme="9" tint="0.799890133365886"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -489,13 +834,255 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -511,41 +1098,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -558,9 +1163,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -818,115 +1420,115 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="19" style="5" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" style="5" customWidth="1"/>
-    <col min="4" max="5" width="14.08203125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="30" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="5" customWidth="1"/>
-    <col min="8" max="8" width="32.58203125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="37.25" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" style="5" customWidth="1"/>
-    <col min="11" max="11" width="36.25" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="19" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
+    <col min="4" max="5" width="14.0833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="30" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.5833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="36.25" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="6"/>
-    </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:12">
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
@@ -952,7 +1554,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" s="1" customFormat="1" spans="1:12">
       <c r="H5" s="1" t="s">
         <v>23</v>
       </c>
@@ -966,7 +1568,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" s="1" customFormat="1" spans="1:12">
       <c r="H6" s="1" t="s">
         <v>25</v>
       </c>
@@ -980,17 +1582,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:12">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" s="1" customFormat="1" spans="1:12">
       <c r="B9" s="1" t="s">
         <v>27</v>
       </c>
@@ -1016,7 +1618,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" s="1" customFormat="1" spans="1:12">
       <c r="H10" s="1" t="s">
         <v>31</v>
       </c>
@@ -1030,7 +1632,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" s="1" customFormat="1" spans="1:12">
       <c r="H11" s="1" t="s">
         <v>33</v>
       </c>
@@ -1044,7 +1646,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" s="1" customFormat="1" spans="1:12">
       <c r="H12" s="1" t="s">
         <v>35</v>
       </c>
@@ -1058,7 +1660,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" s="1" customFormat="1" spans="1:12">
       <c r="H13" s="1" t="s">
         <v>37</v>
       </c>
@@ -1072,7 +1674,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" s="1" customFormat="1" spans="1:12">
       <c r="H14" s="1" t="s">
         <v>39</v>
       </c>
@@ -1086,7 +1688,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" s="1" customFormat="1" spans="1:12">
       <c r="H15" s="1" t="s">
         <v>41</v>
       </c>
@@ -1100,7 +1702,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" s="1" customFormat="1" spans="1:12">
       <c r="H16" s="1" t="s">
         <v>43</v>
       </c>
@@ -1114,7 +1716,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="8:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" s="1" customFormat="1" spans="8:11">
       <c r="H17" s="1" t="s">
         <v>45</v>
       </c>
@@ -1132,16 +1734,17 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
@@ -1150,14 +1753,14 @@
     <col min="5" max="5" width="9" style="1"/>
     <col min="6" max="6" width="31" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="32.08203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.0833333333333" style="1" customWidth="1"/>
     <col min="9" max="9" width="24.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="27.08203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.8333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.0833333333333" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1179,15 +1782,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1213,7 +1816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1243,7 +1846,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
         <v>47</v>
       </c>
@@ -1269,7 +1872,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="H5" s="1" t="s">
         <v>51</v>
       </c>
@@ -1283,7 +1886,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="H6" s="1" t="s">
         <v>53</v>
       </c>
@@ -1297,7 +1900,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="H7" s="1" t="s">
         <v>55</v>
       </c>
@@ -1311,7 +1914,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="H8" s="1" t="s">
         <v>57</v>
       </c>
@@ -1325,7 +1928,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="H9" s="1" t="s">
         <v>59</v>
       </c>
@@ -1343,32 +1946,33 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="49.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="19.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.8333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
     <col min="8" max="8" width="21.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="1"/>
     <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="23.3333333333333" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.75" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1390,15 +1994,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1424,7 +2028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="56" x14ac:dyDescent="0.3">
+    <row r="3" ht="57" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1454,7 +2058,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="B4" s="4" t="s">
         <v>61</v>
       </c>
@@ -1477,7 +2081,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
         <v>65</v>
       </c>
@@ -1492,42 +2096,43 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H4:H1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D1048576" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D1048576">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="40.08203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.0833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="69.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.3333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="42.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="24" style="1" customWidth="1"/>
     <col min="10" max="10" width="14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.08203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.0833333333333" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1549,15 +2154,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1583,7 +2188,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="28" x14ac:dyDescent="0.3">
+    <row r="3" ht="28.5" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1613,7 +2218,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="B4" s="4" t="s">
         <v>67</v>
       </c>
@@ -1639,7 +2244,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="H5" s="4"/>
       <c r="K5" s="4"/>
     </row>
@@ -1647,40 +2252,41 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H4:H5">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J5">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D5" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D5">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="20.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.4140625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="8.66666666666667" style="1"/>
+    <col min="2" max="2" width="20.5833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.4166666666667" style="1" customWidth="1"/>
+    <col min="4" max="5" width="8.66666666666667" style="1"/>
     <col min="6" max="6" width="27.5" style="1" customWidth="1"/>
-    <col min="7" max="8" width="8.6640625" style="1"/>
-    <col min="9" max="9" width="28.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="1"/>
+    <col min="7" max="8" width="8.66666666666667" style="1"/>
+    <col min="9" max="9" width="28.8333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.66666666666667" style="1"/>
     <col min="11" max="11" width="31.25" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="1"/>
+    <col min="12" max="16384" width="8.66666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1702,15 +2308,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1736,7 +2342,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="84" x14ac:dyDescent="0.3">
+    <row r="3" ht="85.5" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1766,7 +2372,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="B4" s="4" t="s">
         <v>71</v>
       </c>
@@ -1792,7 +2398,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
         <v>75</v>
       </c>
@@ -1806,7 +2412,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="H6" s="1" t="s">
         <v>77</v>
       </c>
@@ -1820,7 +2426,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="H7" s="1" t="s">
         <v>79</v>
       </c>
@@ -1834,7 +2440,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="H8" s="1" t="s">
         <v>81</v>
       </c>
@@ -1848,7 +2454,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="H9" s="1" t="s">
         <v>83</v>
       </c>
@@ -1862,7 +2468,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="H10" s="1" t="s">
         <v>85</v>
       </c>
@@ -1876,7 +2482,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="H11" s="1" t="s">
         <v>87</v>
       </c>
@@ -1894,36 +2500,37 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D4" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D4">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="25.4140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.66666666666667" style="1"/>
+    <col min="2" max="2" width="25.4166666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.8333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83333333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="26.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="1"/>
-    <col min="8" max="8" width="56.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.66666666666667" style="1"/>
+    <col min="8" max="8" width="56.1666666666667" style="1" customWidth="1"/>
     <col min="9" max="9" width="39.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="1"/>
-    <col min="11" max="11" width="44.33203125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.6640625" style="1"/>
+    <col min="10" max="10" width="8.66666666666667" style="1"/>
+    <col min="11" max="11" width="44.3333333333333" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.66666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1945,15 +2552,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1979,7 +2586,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="112" x14ac:dyDescent="0.3">
+    <row r="3" ht="128.25" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2009,7 +2616,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="B4" s="4" t="s">
         <v>89</v>
       </c>
@@ -2035,7 +2642,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="H5" s="4" t="s">
         <v>93</v>
       </c>
@@ -2049,7 +2656,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="H6" s="4" t="s">
         <v>95</v>
       </c>
@@ -2063,7 +2670,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="H7" s="4" t="s">
         <v>97</v>
       </c>
@@ -2077,7 +2684,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="H8" s="4" t="s">
         <v>99</v>
       </c>
@@ -2091,7 +2698,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="H9" s="4" t="s">
         <v>101</v>
       </c>
@@ -2105,7 +2712,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="H10" s="4" t="s">
         <v>103</v>
       </c>
@@ -2119,7 +2726,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="H11" s="4" t="s">
         <v>105</v>
       </c>
@@ -2133,7 +2740,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12">
       <c r="H12" s="4" t="s">
         <v>107</v>
       </c>
@@ -2147,7 +2754,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12">
       <c r="H13" s="4" t="s">
         <v>109</v>
       </c>
@@ -2165,31 +2772,32 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="25.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.0833333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1"/>
     <col min="6" max="6" width="26.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
     <col min="8" max="8" width="44.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.8333333333333" style="1" customWidth="1"/>
     <col min="10" max="10" width="23" style="1" customWidth="1"/>
-    <col min="11" max="11" width="37.08203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="37.0833333333333" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2211,15 +2819,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2245,7 +2853,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="70" x14ac:dyDescent="0.3">
+    <row r="3" ht="85.5" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2275,7 +2883,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
         <v>111</v>
       </c>
@@ -2305,31 +2913,32 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="38.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.58203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.08203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.08203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.58333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.0833333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.0833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.0833333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="44.08203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="44.0833333333333" style="1" customWidth="1"/>
     <col min="9" max="9" width="22" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.3333333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="29.75" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2351,15 +2960,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2385,7 +2994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="168" x14ac:dyDescent="0.3">
+    <row r="3" ht="171" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2415,7 +3024,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
         <v>114</v>
       </c>
@@ -2441,7 +3050,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="H5" s="1" t="s">
         <v>118</v>
       </c>
@@ -2455,7 +3064,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="H6" s="1" t="s">
         <v>120</v>
       </c>
@@ -2469,7 +3078,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="H7" s="1" t="s">
         <v>122</v>
       </c>
@@ -2483,7 +3092,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="H8" s="1" t="s">
         <v>124</v>
       </c>
@@ -2497,7 +3106,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="H9" s="1" t="s">
         <v>126</v>
       </c>
@@ -2511,7 +3120,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="H10" s="1" t="s">
         <v>128</v>
       </c>
@@ -2529,7 +3138,157 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <cols>
+    <col min="2" max="2" width="23.875" customWidth="1"/>
+    <col min="4" max="4" width="21.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:12">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:12">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="171" spans="1:12">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H4" t="s">
+        <v>132</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="H5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/Defines/__enums__.xlsx
+++ b/GameConfig/Datas/Defines/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFB3721-BAF2-40A4-8615-61E09B037EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FC4A0A-8A6D-4467-81DB-98BFF9BDAC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1960" yWindow="3880" windowWidth="28800" windowHeight="15380" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2980" yWindow="2410" windowWidth="28800" windowHeight="18470" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="163">
   <si>
     <t>##var</t>
   </si>
@@ -84,6 +84,384 @@
     <t>注释</t>
   </si>
   <si>
+    <t>EGuideType</t>
+  </si>
+  <si>
+    <t>引导类型</t>
+  </si>
+  <si>
+    <t>ForceGuide</t>
+  </si>
+  <si>
+    <t>强引导</t>
+  </si>
+  <si>
+    <t>WeakGuide</t>
+  </si>
+  <si>
+    <t>弱引导</t>
+  </si>
+  <si>
+    <t>EGuideState</t>
+  </si>
+  <si>
+    <t>引导运行状态</t>
+  </si>
+  <si>
+    <t>NotReady</t>
+  </si>
+  <si>
+    <t>未就绪</t>
+  </si>
+  <si>
+    <t>Idle</t>
+  </si>
+  <si>
+    <t>空闲</t>
+  </si>
+  <si>
+    <t>ResolvingTarget</t>
+  </si>
+  <si>
+    <t>解析目标</t>
+  </si>
+  <si>
+    <t>Presenting</t>
+  </si>
+  <si>
+    <t>展示中</t>
+  </si>
+  <si>
+    <t>Waiting</t>
+  </si>
+  <si>
+    <t>等待中</t>
+  </si>
+  <si>
+    <t>Paused</t>
+  </si>
+  <si>
+    <t>已暂停</t>
+  </si>
+  <si>
+    <t>EGuideStepType</t>
+  </si>
+  <si>
+    <t>引导步骤类型</t>
+  </si>
+  <si>
+    <t>Explain</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>ClickTarget</t>
+  </si>
+  <si>
+    <t>点击目标</t>
+  </si>
+  <si>
+    <t>ClickAnywhere</t>
+  </si>
+  <si>
+    <t>任意点击</t>
+  </si>
+  <si>
+    <t>WaitEvent</t>
+  </si>
+  <si>
+    <t>等待事件</t>
+  </si>
+  <si>
+    <t>Delay</t>
+  </si>
+  <si>
+    <t>延时</t>
+  </si>
+  <si>
+    <t>DragHint</t>
+  </si>
+  <si>
+    <t>拖拽提示</t>
+  </si>
+  <si>
+    <t>CustomAction</t>
+  </si>
+  <si>
+    <t>自定义动作</t>
+  </si>
+  <si>
+    <t>EGuideInputMode</t>
+  </si>
+  <si>
+    <t>引导输入模式</t>
+  </si>
+  <si>
+    <t>BlockAll</t>
+  </si>
+  <si>
+    <t>全部拦截</t>
+  </si>
+  <si>
+    <t>PassThroughTarget</t>
+  </si>
+  <si>
+    <t>目标透传</t>
+  </si>
+  <si>
+    <t>AllowAll</t>
+  </si>
+  <si>
+    <t>全部放行</t>
+  </si>
+  <si>
+    <t>EGuideSkipScope</t>
+  </si>
+  <si>
+    <t>引导跳过范围</t>
+  </si>
+  <si>
+    <t>Guide</t>
+  </si>
+  <si>
+    <t>当前引导</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>整个引导组</t>
+  </si>
+  <si>
+    <t>EGuideResumePolicy</t>
+  </si>
+  <si>
+    <t>引导恢复策略</t>
+  </si>
+  <si>
+    <t>RestartGuide</t>
+  </si>
+  <si>
+    <t>重启引导</t>
+  </si>
+  <si>
+    <t>ResumeStep</t>
+  </si>
+  <si>
+    <t>恢复步骤</t>
+  </si>
+  <si>
+    <t>DoNotResume</t>
+  </si>
+  <si>
+    <t>不恢复</t>
+  </si>
+  <si>
+    <t>EGuideFailurePolicy</t>
+  </si>
+  <si>
+    <t>引导故障策略</t>
+  </si>
+  <si>
+    <t>Retry</t>
+  </si>
+  <si>
+    <t>重试</t>
+  </si>
+  <si>
+    <t>SkipStep</t>
+  </si>
+  <si>
+    <t>跳过步骤</t>
+  </si>
+  <si>
+    <t>AbortGuide</t>
+  </si>
+  <si>
+    <t>中止引导</t>
+  </si>
+  <si>
+    <t>EGuideTipPlacement</t>
+  </si>
+  <si>
+    <t>引导提示位置</t>
+  </si>
+  <si>
+    <t>ScreenCenter</t>
+  </si>
+  <si>
+    <t>屏幕中央</t>
+  </si>
+  <si>
+    <t>AboveTarget</t>
+  </si>
+  <si>
+    <t>目标上方</t>
+  </si>
+  <si>
+    <t>BelowTarget</t>
+  </si>
+  <si>
+    <t>目标下方</t>
+  </si>
+  <si>
+    <t>EGuideMaskShape</t>
+  </si>
+  <si>
+    <t>引导遮罩形状，与GuideMask Shader的_MaskType直接对应</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>无遮罩孔</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>圆形</t>
+  </si>
+  <si>
+    <t>Rectangle</t>
+  </si>
+  <si>
+    <t>矩形</t>
+  </si>
+  <si>
+    <t>RoundedRectangle</t>
+  </si>
+  <si>
+    <t>圆角矩形</t>
+  </si>
+  <si>
+    <t>EGuideArrowMoveType</t>
+  </si>
+  <si>
+    <t>引导手指移动类型</t>
+  </si>
+  <si>
+    <t>不显示</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>中间移动到目标位置</t>
+  </si>
+  <si>
+    <t>CustomMove</t>
+  </si>
+  <si>
+    <t>自定义移动方向</t>
+  </si>
+  <si>
+    <t>test.AccessFlag</t>
+  </si>
+  <si>
+    <t>WRITE</t>
+  </si>
+  <si>
+    <t>READ</t>
+  </si>
+  <si>
+    <t>TRUNCATE</t>
+  </si>
+  <si>
+    <t>NEW</t>
+  </si>
+  <si>
+    <t>READ_WRITE</t>
+  </si>
+  <si>
+    <t>WRITE|READ</t>
+  </si>
+  <si>
+    <t>位标记使用示例</t>
+  </si>
+  <si>
+    <t>ColorQuality</t>
+  </si>
+  <si>
+    <t>COLOR_NONE</t>
+  </si>
+  <si>
+    <t>无定义颜色占位</t>
+  </si>
+  <si>
+    <t>COLOR_WHITE</t>
+  </si>
+  <si>
+    <t>白色</t>
+  </si>
+  <si>
+    <t>COLOR_GREEN</t>
+  </si>
+  <si>
+    <t>绿色</t>
+  </si>
+  <si>
+    <t>COLOR_BLUE</t>
+  </si>
+  <si>
+    <t>蓝色</t>
+  </si>
+  <si>
+    <t>COLOR_PURPLE</t>
+  </si>
+  <si>
+    <t>紫色</t>
+  </si>
+  <si>
+    <t>COLOR_ORANGE</t>
+  </si>
+  <si>
+    <t>橙色</t>
+  </si>
+  <si>
+    <t>COLOR_RED</t>
+  </si>
+  <si>
+    <t>红色</t>
+  </si>
+  <si>
+    <t>COLOR_CAI</t>
+  </si>
+  <si>
+    <t>彩色</t>
+  </si>
+  <si>
+    <t>COLOR_MAX</t>
+  </si>
+  <si>
+    <t>最大品质，新增+1</t>
+  </si>
+  <si>
+    <t>SysSoundID</t>
+  </si>
+  <si>
+    <t>BGM</t>
+  </si>
+  <si>
+    <t>背景音乐</t>
+  </si>
+  <si>
+    <t>BTN_CLICK</t>
+  </si>
+  <si>
+    <t>按钮点击</t>
+  </si>
+  <si>
+    <t>CommonEffectID</t>
+  </si>
+  <si>
+    <t>COMMON_EFFECT_1</t>
+  </si>
+  <si>
+    <t>特效1</t>
+  </si>
+  <si>
     <t>LocalAreaType</t>
   </si>
   <si>
@@ -136,410 +514,6 @@
   </si>
   <si>
     <t>占位符（新增+1）</t>
-  </si>
-  <si>
-    <t>EGuideState</t>
-  </si>
-  <si>
-    <t>引导运行状态</t>
-  </si>
-  <si>
-    <t>NotReady</t>
-  </si>
-  <si>
-    <t>未就绪</t>
-  </si>
-  <si>
-    <t>Idle</t>
-  </si>
-  <si>
-    <t>空闲</t>
-  </si>
-  <si>
-    <t>ResolvingTarget</t>
-  </si>
-  <si>
-    <t>解析目标</t>
-  </si>
-  <si>
-    <t>Presenting</t>
-  </si>
-  <si>
-    <t>展示中</t>
-  </si>
-  <si>
-    <t>Waiting</t>
-  </si>
-  <si>
-    <t>等待中</t>
-  </si>
-  <si>
-    <t>Paused</t>
-  </si>
-  <si>
-    <t>已暂停</t>
-  </si>
-  <si>
-    <t>引导步骤类型</t>
-  </si>
-  <si>
-    <t>Explain</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>点击目标</t>
-  </si>
-  <si>
-    <t>ClickAnywhere</t>
-  </si>
-  <si>
-    <t>任意点击</t>
-  </si>
-  <si>
-    <t>等待事件</t>
-  </si>
-  <si>
-    <t>Delay</t>
-  </si>
-  <si>
-    <t>延时</t>
-  </si>
-  <si>
-    <t>DragHint</t>
-  </si>
-  <si>
-    <t>拖拽提示</t>
-  </si>
-  <si>
-    <t>自定义动作</t>
-  </si>
-  <si>
-    <t>引导输入模式</t>
-  </si>
-  <si>
-    <t>BlockAll</t>
-  </si>
-  <si>
-    <t>全部拦截</t>
-  </si>
-  <si>
-    <t>PassThroughTarget</t>
-  </si>
-  <si>
-    <t>目标透传</t>
-  </si>
-  <si>
-    <t>AllowAll</t>
-  </si>
-  <si>
-    <t>全部放行</t>
-  </si>
-  <si>
-    <t>EGuideSkipScope</t>
-  </si>
-  <si>
-    <t>引导跳过范围</t>
-  </si>
-  <si>
-    <t>Guide</t>
-  </si>
-  <si>
-    <t>当前引导</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>整个引导组</t>
-  </si>
-  <si>
-    <t>EGuideResumePolicy</t>
-  </si>
-  <si>
-    <t>引导恢复策略</t>
-  </si>
-  <si>
-    <t>重启引导</t>
-  </si>
-  <si>
-    <t>ResumeStep</t>
-  </si>
-  <si>
-    <t>恢复步骤</t>
-  </si>
-  <si>
-    <t>不恢复</t>
-  </si>
-  <si>
-    <t>EGuideFailurePolicy</t>
-  </si>
-  <si>
-    <t>引导故障策略</t>
-  </si>
-  <si>
-    <t>Retry</t>
-  </si>
-  <si>
-    <t>重试</t>
-  </si>
-  <si>
-    <t>SkipStep</t>
-  </si>
-  <si>
-    <t>跳过步骤</t>
-  </si>
-  <si>
-    <t>AbortGuide</t>
-  </si>
-  <si>
-    <t>中止引导</t>
-  </si>
-  <si>
-    <t>EGuideTipPlacement</t>
-  </si>
-  <si>
-    <t>引导提示位置</t>
-  </si>
-  <si>
-    <t>ScreenCenter</t>
-  </si>
-  <si>
-    <t>屏幕中央</t>
-  </si>
-  <si>
-    <t>目标上方</t>
-  </si>
-  <si>
-    <t>目标下方</t>
-  </si>
-  <si>
-    <t>EGuideMaskShape</t>
-  </si>
-  <si>
-    <t>引导遮罩形状，与GuideMask Shader的_MaskType直接对应</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>无遮罩孔</t>
-  </si>
-  <si>
-    <t>Circle</t>
-  </si>
-  <si>
-    <t>圆形</t>
-  </si>
-  <si>
-    <t>Rectangle</t>
-  </si>
-  <si>
-    <t>矩形</t>
-  </si>
-  <si>
-    <t>RoundedRectangle</t>
-  </si>
-  <si>
-    <t>圆角矩形</t>
-  </si>
-  <si>
-    <t>test.AccessFlag</t>
-  </si>
-  <si>
-    <t>WRITE</t>
-  </si>
-  <si>
-    <t>READ</t>
-  </si>
-  <si>
-    <t>TRUNCATE</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>READ_WRITE</t>
-  </si>
-  <si>
-    <t>WRITE|READ</t>
-  </si>
-  <si>
-    <t>位标记使用示例</t>
-  </si>
-  <si>
-    <t>ColorQuality</t>
-  </si>
-  <si>
-    <t>COLOR_NONE</t>
-  </si>
-  <si>
-    <t>无定义颜色占位</t>
-  </si>
-  <si>
-    <t>COLOR_WHITE</t>
-  </si>
-  <si>
-    <t>白色</t>
-  </si>
-  <si>
-    <t>COLOR_GREEN</t>
-  </si>
-  <si>
-    <t>绿色</t>
-  </si>
-  <si>
-    <t>COLOR_BLUE</t>
-  </si>
-  <si>
-    <t>蓝色</t>
-  </si>
-  <si>
-    <t>COLOR_PURPLE</t>
-  </si>
-  <si>
-    <t>紫色</t>
-  </si>
-  <si>
-    <t>COLOR_ORANGE</t>
-  </si>
-  <si>
-    <t>橙色</t>
-  </si>
-  <si>
-    <t>COLOR_RED</t>
-  </si>
-  <si>
-    <t>红色</t>
-  </si>
-  <si>
-    <t>COLOR_CAI</t>
-  </si>
-  <si>
-    <t>彩色</t>
-  </si>
-  <si>
-    <t>COLOR_MAX</t>
-  </si>
-  <si>
-    <t>最大品质，新增+1</t>
-  </si>
-  <si>
-    <t>SysSoundID</t>
-  </si>
-  <si>
-    <t>BGM</t>
-  </si>
-  <si>
-    <t>背景音乐</t>
-  </si>
-  <si>
-    <t>BTN_CLICK</t>
-  </si>
-  <si>
-    <t>按钮点击</t>
-  </si>
-  <si>
-    <t>CommonEffectID</t>
-  </si>
-  <si>
-    <t>COMMON_EFFECT_1</t>
-  </si>
-  <si>
-    <t>特效1</t>
-  </si>
-  <si>
-    <t>EGuideInputMode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EGuideType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>引导类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ForceGuide</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强引导</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弱引导</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeakGuide</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EGuideArrowMoveType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>引导手指移动类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不显示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中间移动到目标位置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CustomMove</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自定义移动方向</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AboveTarget</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BelowTarget</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClickTarget</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EGuideStepType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CustomAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WaitEvent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RestartGuide</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DoNotResume</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -555,18 +529,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -636,43 +609,38 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -980,7 +948,7 @@
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9" style="6"/>
+    <col min="1" max="1" width="9" style="6" customWidth="1"/>
     <col min="2" max="2" width="19" style="8" customWidth="1"/>
     <col min="3" max="3" width="20.83203125" style="8" customWidth="1"/>
     <col min="4" max="5" width="14.08203125" style="8" customWidth="1"/>
@@ -990,10 +958,11 @@
     <col min="9" max="9" width="5.25" style="8" customWidth="1"/>
     <col min="10" max="10" width="12.08203125" style="8" customWidth="1"/>
     <col min="11" max="11" width="15.08203125" style="8" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="6"/>
+    <col min="12" max="12" width="9" style="6" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1015,13 +984,13 @@
       <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="12"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -1081,7 +1050,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B4" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C4" s="6" t="b">
         <v>1</v>
@@ -1090,7 +1059,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J4" s="6">
         <v>1</v>
@@ -1098,7 +1067,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H5" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J5" s="6">
         <v>2</v>
@@ -1106,7 +1075,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H6" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J6" s="6">
         <v>4</v>
@@ -1114,7 +1083,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H7" s="6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J7" s="6">
         <v>8</v>
@@ -1122,20 +1091,20 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="H8" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1157,11 +1126,11 @@
     <col min="10" max="10" width="37.33203125" style="4" customWidth="1"/>
     <col min="11" max="11" width="38.58203125" style="4" customWidth="1"/>
     <col min="12" max="12" width="33.58203125" style="4" customWidth="1"/>
-    <col min="13" max="13" width="9" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="4"/>
+    <col min="13" max="14" width="9" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1183,13 +1152,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="12"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1249,7 +1218,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C4" s="4" t="b">
         <v>0</v>
@@ -1258,135 +1227,135 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J4" s="4">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H6" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J6" s="4">
         <v>2</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J7" s="4">
         <v>3</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H8" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J8" s="4">
         <v>4</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H9" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J9" s="4">
         <v>5</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H10" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J10" s="4">
         <v>6</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H11" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J11" s="4">
         <v>7</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H12" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J12" s="4">
         <v>8</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1400,17 +1369,18 @@
     <col min="2" max="2" width="49.5" style="4" customWidth="1"/>
     <col min="3" max="3" width="26.25" style="4" customWidth="1"/>
     <col min="4" max="4" width="27" style="4" customWidth="1"/>
-    <col min="5" max="7" width="9" style="4" customWidth="1"/>
+    <col min="5" max="5" width="9" style="4" customWidth="1"/>
+    <col min="6" max="7" width="12.5" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.75" style="4" customWidth="1"/>
     <col min="9" max="9" width="9" style="4" customWidth="1"/>
     <col min="10" max="10" width="19.5" style="4" customWidth="1"/>
     <col min="11" max="11" width="23.33203125" style="4" customWidth="1"/>
     <col min="12" max="12" width="19.75" style="4" customWidth="1"/>
-    <col min="13" max="13" width="9" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="4"/>
+    <col min="13" max="14" width="9" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1432,13 +1402,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="12"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1498,7 +1468,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C4" s="4" t="b">
         <v>0</v>
@@ -1507,36 +1477,36 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="J4" s="4">
         <v>1000001</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H5" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J5" s="4">
         <v>1000002</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H4:H1048576">
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D1048576" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -1563,11 +1533,11 @@
     <col min="9" max="9" width="24" style="4" customWidth="1"/>
     <col min="10" max="10" width="14" style="4" customWidth="1"/>
     <col min="11" max="11" width="18.08203125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="9" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="4"/>
+    <col min="12" max="13" width="9" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1589,13 +1559,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="12"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1655,7 +1625,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C4" s="4" t="b">
         <v>0</v>
@@ -1664,23 +1634,23 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="J4" s="4">
         <v>1</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H4:H5">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
@@ -1710,11 +1680,11 @@
     <col min="9" max="9" width="28.83203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.6640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="31.25" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="1"/>
+    <col min="12" max="13" width="8.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1736,15 +1706,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="13"/>
-    </row>
-    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="12"/>
+    </row>
+    <row r="2" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1800,10 +1770,10 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="C4" s="4" t="b">
         <v>0</v>
@@ -1815,20 +1785,20 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="J4" s="4">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1837,20 +1807,20 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>23</v>
+        <v>149</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>23</v>
+        <v>149</v>
       </c>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1859,20 +1829,20 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="J6" s="4">
         <v>2</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1881,20 +1851,20 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>26</v>
+        <v>152</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>27</v>
+        <v>153</v>
       </c>
       <c r="J7" s="4">
         <v>3</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>27</v>
+        <v>153</v>
       </c>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1903,20 +1873,20 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="J8" s="4">
         <v>4</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1925,20 +1895,20 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>30</v>
+        <v>156</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
       <c r="J9" s="4">
         <v>5</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1947,20 +1917,20 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="J10" s="4">
         <v>6</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1969,16 +1939,16 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="J11" s="4">
         <v>7</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>36</v>
+        <v>162</v>
       </c>
       <c r="L11" s="4"/>
     </row>
@@ -1986,7 +1956,7 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:D4" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -1997,20 +1967,20 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB5337A-2CF2-4276-B4F8-E8CC7340429D}">
-  <dimension ref="A1:L40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="51.08203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.4140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="51.08203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.4140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.4140625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2032,15 +2002,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="11"/>
-    </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="12"/>
+    </row>
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2096,10 +2066,10 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4" t="b">
         <v>0</v>
@@ -2110,21 +2080,21 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2133,21 +2103,21 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>146</v>
+        <v>24</v>
       </c>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="b">
         <v>0</v>
@@ -2158,21 +2128,21 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4">
         <v>0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2181,18 +2151,18 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4">
         <v>1</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2201,18 +2171,18 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4">
         <v>2</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2221,18 +2191,18 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4">
         <v>3</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2241,18 +2211,18 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4">
         <v>4</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2261,21 +2231,21 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4">
         <v>5</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="C12" s="4" t="b">
         <v>0</v>
@@ -2286,21 +2256,21 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4">
         <v>0</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -2309,18 +2279,18 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -2329,18 +2299,18 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4">
         <v>2</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2349,18 +2319,18 @@
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4">
         <v>3</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -2369,18 +2339,18 @@
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4">
         <v>4</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -2389,18 +2359,18 @@
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4">
         <v>5</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2409,21 +2379,21 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4">
         <v>6</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="C19" s="4" t="b">
         <v>0</v>
@@ -2434,21 +2404,21 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4">
         <v>0</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -2457,18 +2427,18 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4">
         <v>1</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -2477,21 +2447,21 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4">
         <v>2</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C22" s="4" t="b">
         <v>0</v>
@@ -2502,21 +2472,21 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4">
         <v>0</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -2525,21 +2495,21 @@
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4">
         <v>1</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C24" s="4" t="b">
         <v>0</v>
@@ -2550,21 +2520,21 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>162</v>
+        <v>71</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4">
         <v>0</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2573,18 +2543,18 @@
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4">
         <v>1</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -2593,21 +2563,21 @@
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4">
         <v>2</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C27" s="4" t="b">
         <v>0</v>
@@ -2618,21 +2588,21 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4">
         <v>0</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -2641,18 +2611,18 @@
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4">
         <v>1</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2661,21 +2631,21 @@
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4">
         <v>2</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C30" s="4" t="b">
         <v>0</v>
@@ -2686,21 +2656,21 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4">
         <v>0</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -2709,18 +2679,18 @@
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -2729,21 +2699,21 @@
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4">
         <v>2</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C33" s="4" t="b">
         <v>0</v>
@@ -2754,21 +2724,21 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4">
         <v>0</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -2777,18 +2747,18 @@
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4">
         <v>1</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -2797,18 +2767,18 @@
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4">
         <v>2</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -2817,21 +2787,21 @@
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4">
         <v>3</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="C37" s="4" t="b">
         <v>0</v>
@@ -2842,21 +2812,21 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4">
         <v>0</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -2865,18 +2835,18 @@
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>152</v>
+        <v>106</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4">
         <v>1</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2885,18 +2855,18 @@
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4">
         <v>2</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" spans="1:12" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -2910,11 +2880,20 @@
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K41"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K42"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K43"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/Defines/__enums__.xlsx
+++ b/GameConfig/Datas/Defines/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87472CDF-E254-405E-9365-484244C14B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E93704C-A1CD-46B6-A4E4-6F59BA4090D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="229">
   <si>
     <t>##var</t>
   </si>
@@ -726,13 +726,17 @@
   </si>
   <si>
     <t>自定义移动方向</t>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -743,6 +747,14 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -790,7 +802,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -804,6 +816,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1500,7 +1515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="168" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1540,6 +1555,9 @@
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E4" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="G4" s="1" t="s">
         <v>138</v>
       </c>
@@ -1574,6 +1592,9 @@
       <c r="D6" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E6" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="G6" s="1" t="s">
         <v>144</v>
       </c>
@@ -1652,6 +1673,9 @@
       <c r="D12" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E12" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="G12" s="1" t="s">
         <v>158</v>
       </c>
@@ -1741,6 +1765,9 @@
       <c r="D19" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E19" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="G19" s="1" t="s">
         <v>174</v>
       </c>
@@ -1786,6 +1813,9 @@
       <c r="D22" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E22" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="G22" s="1" t="s">
         <v>182</v>
       </c>
@@ -1820,6 +1850,9 @@
       <c r="D24" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E24" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="G24" s="1" t="s">
         <v>188</v>
       </c>
@@ -1865,6 +1898,9 @@
       <c r="D27" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E27" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="G27" s="1" t="s">
         <v>196</v>
       </c>
@@ -1910,6 +1946,9 @@
       <c r="D30" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E30" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="G30" s="1" t="s">
         <v>204</v>
       </c>
@@ -1955,6 +1994,9 @@
       <c r="D33" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="E33" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="G33" s="1" t="s">
         <v>212</v>
       </c>
@@ -2010,6 +2052,9 @@
       </c>
       <c r="D37" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>222</v>
